--- a/documentation/Construccion y Evolucion/2. Reportes de problemas/PR 6.xlsx
+++ b/documentation/Construccion y Evolucion/2. Reportes de problemas/PR 6.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\TraductorBraille\documentation\Construccion y Evolucion\2. Reportes de problemas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\EPN\SEXTO SEMESTRE\Construccion y evolucion software\traductor_braile_español\TraductorBrailleEspanol\documentation\Construccion y Evolucion\2. Reportes de problemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2B6644-C6DC-453E-809C-E9BB8AE5E5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="PR Formato" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="16">
   <si>
     <t>Reporte de Problema</t>
   </si>
@@ -64,13 +63,22 @@
   </si>
   <si>
     <t xml:space="preserve">No se validan adecuadamente todos los posibles caracteres no válidos, lo que puede causar errores en la traducción. </t>
+  </si>
+  <si>
+    <t>Los caracteres que no se encuentran presentes en el diccionario de español-braille son ignorados, por lo que el usuario no va a tener presente cuando un caracter no es interpretado.</t>
+  </si>
+  <si>
+    <t>Controlar que los caracteres  que no se encuentren presentes en el diccionario sean presentados de alguna manera en la traducción, y adicionalmente dejar explicito en el programa que significa dicho carácter para que el usuario este enterado cuando un caracter no puede ser traducido.</t>
+  </si>
+  <si>
+    <t>Inicialmente este no se consideraba un problema, debido a que se pensó en un principio que para mantener una traducción lógica en braille se debía ignorar cualquier carácter que no se pueda traducir, debido a que esto podía generar confusión para los usuarios que puedan leer el texto braille.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -714,21 +722,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F84A08-0160-4953-9528-DB07A5F993CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:H28"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.5703125" customWidth="1"/>
-    <col min="5" max="7" width="20.140625" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.625" customWidth="1"/>
+    <col min="3" max="3" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.625" customWidth="1"/>
+    <col min="5" max="7" width="20.125" customWidth="1"/>
+    <col min="8" max="8" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" ht="15" thickBot="1">
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8">
       <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
@@ -751,7 +759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" ht="18">
       <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
@@ -768,7 +776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8">
       <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
@@ -781,7 +789,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8">
       <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
@@ -794,7 +802,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8">
       <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
@@ -807,7 +815,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8">
       <c r="B7" s="6" t="s">
         <v>8</v>
       </c>
@@ -824,7 +832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8">
       <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
@@ -837,7 +845,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8">
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
@@ -850,7 +858,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8">
       <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
@@ -867,7 +875,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8">
       <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
@@ -880,7 +888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8">
       <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
@@ -893,7 +901,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8">
       <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
@@ -908,7 +916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8">
       <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
@@ -923,7 +931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8">
       <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
@@ -936,7 +944,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8">
       <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
@@ -949,7 +957,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8">
       <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
@@ -964,12 +972,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8">
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -979,7 +987,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8">
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
@@ -992,7 +1000,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8">
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
@@ -1005,7 +1013,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8">
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
@@ -1020,12 +1028,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8">
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
@@ -1035,7 +1043,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" ht="28.5" customHeight="1">
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
@@ -1048,7 +1056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8">
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
@@ -1061,7 +1069,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8">
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
@@ -1084,12 +1092,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="44.25" customHeight="1">
       <c r="B26" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D26" s="28"/>
       <c r="E26" s="28"/>
@@ -1099,7 +1107,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" ht="15" thickBot="1">
       <c r="B27" s="11" t="s">
         <v>8</v>
       </c>
@@ -1122,17 +1130,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8">
       <c r="H28" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="D7:G7"/>
     <mergeCell ref="D10:G10"/>
     <mergeCell ref="C14:G15"/>
     <mergeCell ref="C18:G19"/>
     <mergeCell ref="C22:G23"/>
     <mergeCell ref="C26:G26"/>
-    <mergeCell ref="D7:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
